--- a/outputs/eims-testcases-20260617/テストケース仕様書兼結果報告書(EIMS)_2026仕様.xlsx
+++ b/outputs/eims-testcases-20260617/テストケース仕様書兼結果報告書(EIMS)_2026仕様.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0001(一覧・詳細表示)" sheetId="1" r:id="R84a11801fbc047b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0002(検索機能)" sheetId="2" r:id="R3dceb0a63f8c4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0003(登録機能)" sheetId="3" r:id="R63582258ba3147af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0004(変更機能)" sheetId="4" r:id="Rc721ae864f4f439b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0005(削除機能)" sheetId="5" r:id="Re1dc24de77074336"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0006(コンポーネント任意)" sheetId="6" r:id="Ra56b3bcfd6b14d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0001(一覧・詳細表示)" sheetId="1" r:id="Rf8aa3cca7d334561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0002(検索機能)" sheetId="2" r:id="Ra927d8004d894269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0003(登録機能)" sheetId="3" r:id="Rc80cc40d1f4c4175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0004(変更機能)" sheetId="4" r:id="R6ee18fd8cfa24064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0005(削除機能)" sheetId="5" r:id="R00db0177c5ff4f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T0006(コンポーネント任意)" sheetId="6" r:id="R64337b1984f5451e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -336,9 +336,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -553,7 +553,7 @@
         <x:v>更新日</x:v>
       </x:c>
       <x:c r="I3" s="18" t="str">
-        <x:v>2026/06/17</x:v>
+        <x:v>2026/07/16</x:v>
       </x:c>
       <x:c r="J3" s="18" t="str">
         <x:v>更新者</x:v>
@@ -624,7 +624,7 @@
         <x:v>トップページが正常に表示され、「社員一覧」「検索」「登録」へ遷移できる導線が表示される。</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>10.1 URLマッピング: GET / -&gt; index</x:v>
+        <x:v>10.1 URLマッピング: GET / -&gt; index／Playwright 検索機能 TC030</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str"/>
       <x:c r="I6" s="14" t="str"/>
@@ -655,7 +655,7 @@
         <x:v>社員一覧画面 employee_list が表示される。</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>UC001 基本フロー、GET /employeeList</x:v>
+        <x:v>UC001 基本フロー、GET /employeeList／Playwright 検索機能 TC031</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str"/>
       <x:c r="I7" s="14" t="str"/>
@@ -686,7 +686,7 @@
         <x:v>社員テーブルの全社員（初期データは10001〜10020の20件）が一覧表示される。</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>6.4 初期データ仕様。削除済みデータがある場合は事前に初期状態へ戻す。</x:v>
+        <x:v>6.4 初期データ仕様。削除済みデータがある場合は事前に初期状態へ戻す。／Playwright 検索機能 TC032</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str"/>
       <x:c r="I8" s="14" t="str"/>
@@ -717,7 +717,7 @@
         <x:v>表は「社員番号」「氏名+カナ」「性別」「部署名」の4列で構成される。</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>1.1.3 一覧画面（共通ルール）</x:v>
+        <x:v>1.1.3 一覧画面（共通ルール）／Playwright 検索機能 TC033</x:v>
       </x:c>
       <x:c r="H9" s="14" t="str"/>
       <x:c r="I9" s="14" t="str"/>
@@ -748,7 +748,7 @@
         <x:v>「氏 名 (氏カナ 名カナ)」形式で表示され、姓・名、氏カナ・名カナの間が半角スペースで連結される。</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>1.1.3 共通の表示ルール</x:v>
+        <x:v>1.1.3 共通の表示ルール／Playwright 検索機能 TC034</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str"/>
       <x:c r="I10" s="14" t="str"/>
@@ -779,7 +779,7 @@
         <x:v>gender=1は「男性」、gender=2は「女性」と表示される。</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>1.1.3 一覧画面（共通ルール）</x:v>
+        <x:v>1.1.3 一覧画面（共通ルール）／Playwright 検索機能 TC035</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str"/>
       <x:c r="I11" s="14" t="str"/>
@@ -810,7 +810,7 @@
         <x:v>部署列には「人事部」「経理部」「営業部」「総務部」「開発部」「企画部」など部署名が表示される。</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>標準実装。簡略化実装の場合は部署コード表示も許容対象として別途判定。</x:v>
+        <x:v>標準実装。簡略化実装の場合は部署コード表示も許容対象として別途判定。／Playwright 検索機能 TC036</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str"/>
       <x:c r="I12" s="14" t="str"/>
@@ -841,7 +841,7 @@
         <x:v>社員詳細画面 employee_detail が表示され、選択した社員番号10001の情報が表示される。</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>UC001 alt3-1、GET /detail/{empNo}</x:v>
+        <x:v>UC001 alt3-1、GET /detail/{empNo}／Playwright 検索機能 TC037</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str"/>
       <x:c r="I13" s="14" t="str"/>
@@ -872,7 +872,7 @@
         <x:v>社員番号、氏、名、氏（カナ）、名（カナ）、性別、部署名が表示される。</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>1.1.3 社員詳細画面</x:v>
+        <x:v>1.1.3 社員詳細画面／Playwright 検索機能 TC038</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str"/>
       <x:c r="I14" s="14" t="str"/>
@@ -903,7 +903,7 @@
         <x:v>選択社員の変更画面 change が表示される。</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>1.1.3、UC004の起点</x:v>
+        <x:v>1.1.3、UC004の起点／Playwright 検索機能 TC039</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str"/>
       <x:c r="I15" s="14" t="str"/>
@@ -934,7 +934,7 @@
         <x:v>選択社員の削除確認画面 delete_confirm が表示される。</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>1.1.3、UC005の起点</x:v>
+        <x:v>1.1.3、UC005の起点／Playwright 検索機能 TC040</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str"/>
       <x:c r="I16" s="14" t="str"/>
@@ -965,7 +965,7 @@
         <x:v>トップページが正常に表示される。</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>UC001 alt3-2</x:v>
+        <x:v>UC001 alt3-2／Playwright 検索機能 TC041</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str"/>
       <x:c r="I17" s="14" t="str"/>
@@ -996,7 +996,7 @@
         <x:v>検索画面 search が表示される。</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>UC001 alt3-3。ボタン名は実装画面の文言に合わせて確認する。</x:v>
+        <x:v>UC001 alt3-3。ボタン名は実装画面の文言に合わせて確認する。／Playwright 検索機能 TC042</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str"/>
       <x:c r="I18" s="14" t="str"/>
@@ -1024,7 +1024,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2426ee0c600485a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaeb19dbf4144646"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1848,7 +1848,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23a77bf0355548d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1662725bb6424f18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2734,7 +2734,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c69329143584d55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9ef1beeda2e4f31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3620,7 +3620,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd26b5dce6e6340cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab1f4c9954f4472a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4103,7 +4103,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0504a2936d643df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R185556e4cbf9440c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4958,7 +4958,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bd596a6fb414639"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd67d78c14a4ea8"/>
   </x:tableParts>
 </x:worksheet>
 </file>